--- a/StructureDefinition-intraocular-pressure.xlsx
+++ b/StructureDefinition-intraocular-pressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T17:43:23+00:00</t>
+    <t>2026-09-11T00:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1208,7 +1208,7 @@
     <t>Observation.method</t>
   </si>
   <si>
-    <t>The tonometry method used (e.g. applanation, non-contact)</t>
+    <t>The tonometry method used (e.g. applanation, non-contact) — LOINC 79764-7</t>
   </si>
   <si>
     <t>Indicates the mechanism used to perform the observation.</t>

--- a/StructureDefinition-intraocular-pressure.xlsx
+++ b/StructureDefinition-intraocular-pressure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T00:16:12+00:00</t>
+    <t>2026-10-19T22:17:00-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -286,7 +286,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}inv-iop-range:IOP value must be between 0 and 80 mmHg {valueQuantity.value &gt;= 0 and valueQuantity.value &lt;= 80}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}inv-iop-range:IOP value must be between 0 and 80 mmHg {value.ofType(Quantity).value.empty() or (value.ofType(Quantity).value &gt;= 0 and value.ofType(Quantity).value &lt;= 80)}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1913,17 +1913,17 @@
   <dimension ref="A1:AP60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.57421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.25390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.77734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="129.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1932,28 +1932,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.2734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.55078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-intraocular-pressure.xlsx
+++ b/StructureDefinition-intraocular-pressure.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2338" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2377" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:17:00-03:00</t>
+    <t>2026-10-20T20:13:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -630,6 +630,31 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:exam</t>
+  </si>
+  <si>
+    <t>exam</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -641,18 +666,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -1073,9 +1086,6 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -1085,7 +1095,7 @@
     <t>bodySiteEye</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.3.0}
 </t>
   </si>
   <si>
@@ -1910,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP60"/>
+  <dimension ref="A1:AP61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.25390625" customWidth="true" bestFit="true"/>
@@ -3646,7 +3656,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>191</v>
       </c>
@@ -3696,7 +3706,7 @@
         <v>83</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>83</v>
@@ -3714,25 +3724,23 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>83</v>
-      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>191</v>
@@ -3759,10 +3767,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3770,14 +3778,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>203</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3793,22 +3803,22 @@
         <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3818,7 +3828,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3833,13 +3843,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>209</v>
+        <v>118</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3857,13 +3867,13 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
@@ -3872,34 +3882,34 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3918,19 +3928,19 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -3940,7 +3950,7 @@
         <v>83</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>83</v>
@@ -3955,13 +3965,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -3979,10 +3989,10 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>94</v>
@@ -3994,30 +4004,30 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>83</v>
+        <v>221</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4025,13 +4035,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>83</v>
@@ -4040,18 +4050,20 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -4099,13 +4111,13 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>83</v>
@@ -4114,44 +4126,44 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>83</v>
+        <v>228</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>235</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>83</v>
@@ -4160,20 +4172,18 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>240</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4221,13 +4231,13 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
@@ -4236,19 +4246,19 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>241</v>
+        <v>83</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4256,14 +4266,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4282,19 +4292,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4343,7 +4353,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4358,34 +4368,34 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>250</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4395,7 +4405,7 @@
         <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>83</v>
@@ -4404,18 +4414,20 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
@@ -4463,7 +4475,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4478,30 +4490,30 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>83</v>
+        <v>256</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4512,10 +4524,10 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>83</v>
@@ -4524,18 +4536,18 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
@@ -4583,13 +4595,13 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
@@ -4598,19 +4610,19 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>269</v>
+        <v>83</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
@@ -4618,10 +4630,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4629,10 +4641,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>95</v>
@@ -4644,19 +4656,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4705,45 +4715,45 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>83</v>
+        <v>273</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>83</v>
+        <v>276</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>283</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4751,34 +4761,34 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -4803,13 +4813,13 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -4827,7 +4837,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4836,7 +4846,7 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>106</v>
@@ -4845,38 +4855,38 @@
         <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>83</v>
+        <v>284</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -4891,16 +4901,16 @@
         <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4925,13 +4935,13 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -4949,16 +4959,16 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
@@ -4967,31 +4977,31 @@
         <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>302</v>
+        <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>303</v>
+        <v>137</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>305</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5001,7 +5011,7 @@
         <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>83</v>
@@ -5010,19 +5020,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>307</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5047,13 +5057,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5071,7 +5081,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5089,27 +5099,27 @@
         <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5120,7 +5130,7 @@
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>95</v>
@@ -5132,18 +5142,20 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>192</v>
+        <v>311</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
@@ -5167,13 +5179,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5191,13 +5203,13 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>83</v>
@@ -5209,27 +5221,27 @@
         <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>320</v>
+        <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5243,7 +5255,7 @@
         <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>
@@ -5252,15 +5264,17 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>325</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5285,13 +5299,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5309,7 +5323,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5321,44 +5335,44 @@
         <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>83</v>
@@ -5370,17 +5384,15 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M29" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5417,73 +5429,71 @@
         <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AC29" t="s" s="2">
+      <c r="AG29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AD29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AF29" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>336</v>
-      </c>
       <c r="B30" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>83</v>
@@ -5492,15 +5502,17 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>338</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>339</v>
+        <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5537,19 +5549,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5573,7 +5585,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5582,14 +5594,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5601,7 +5615,7 @@
         <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>83</v>
@@ -5610,13 +5624,13 @@
         <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5667,19 +5681,19 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>83</v>
@@ -5691,7 +5705,7 @@
         <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>329</v>
+        <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5702,10 +5716,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5716,7 +5730,7 @@
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5728,13 +5742,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5773,43 +5787,43 @@
         <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AC32" t="s" s="2">
+      <c r="AG32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5820,10 +5834,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5831,10 +5845,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5846,24 +5860,22 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>351</v>
-      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>83</v>
@@ -5893,31 +5905,31 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -5929,7 +5941,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -5940,10 +5952,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5966,22 +5978,24 @@
         <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>356</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>83</v>
+        <v>355</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6023,10 +6037,10 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>94</v>
@@ -6035,7 +6049,7 @@
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>83</v>
@@ -6058,10 +6072,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6069,10 +6083,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6081,23 +6095,19 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>365</v>
-      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6145,13 +6155,13 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
@@ -6166,10 +6176,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>367</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>368</v>
+        <v>137</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6180,10 +6190,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6194,7 +6204,7 @@
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6206,19 +6216,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>325</v>
+        <v>364</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6267,13 +6277,13 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
@@ -6288,10 +6298,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6300,12 +6310,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6319,28 +6329,28 @@
         <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J37" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>329</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6365,13 +6375,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6410,10 +6420,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6422,12 +6432,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6441,7 +6451,7 @@
         <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>83</v>
@@ -6450,18 +6460,20 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>387</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6485,13 +6497,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6509,7 +6521,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6527,27 +6539,27 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6570,16 +6582,16 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6629,7 +6641,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6647,27 +6659,27 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6678,7 +6690,7 @@
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>83</v>
@@ -6690,20 +6702,18 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6751,45 +6761,45 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AG40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>411</v>
-      </c>
       <c r="AN40" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6800,7 +6810,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -6812,16 +6822,20 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>325</v>
+        <v>408</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>326</v>
+        <v>409</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -6869,19 +6883,19 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>328</v>
+        <v>407</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>83</v>
+        <v>413</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>83</v>
@@ -6890,10 +6904,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>83</v>
+        <v>414</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>329</v>
+        <v>415</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -6904,21 +6918,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6930,17 +6944,15 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -6989,19 +7001,19 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -7013,7 +7025,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7024,14 +7036,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>416</v>
+        <v>139</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7044,26 +7056,24 @@
         <v>83</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>417</v>
+        <v>141</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>418</v>
+        <v>335</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O43" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7111,7 +7121,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7135,7 +7145,7 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7146,42 +7156,46 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L44" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7229,19 +7243,19 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7250,10 +7264,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>425</v>
+        <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>426</v>
+        <v>137</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7264,10 +7278,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7290,13 +7304,13 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7347,7 +7361,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7356,7 +7370,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7368,10 +7382,10 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7382,10 +7396,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7408,20 +7422,16 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>192</v>
+        <v>424</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>435</v>
-      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7445,13 +7455,13 @@
         <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>436</v>
+        <v>83</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>437</v>
+        <v>83</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
@@ -7469,7 +7479,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7478,7 +7488,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>83</v>
+        <v>427</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7487,13 +7497,13 @@
         <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>438</v>
+        <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>304</v>
+        <v>433</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7504,10 +7514,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7518,7 +7528,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -7533,16 +7543,16 @@
         <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7567,13 +7577,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>209</v>
+        <v>118</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7591,13 +7601,13 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
@@ -7609,13 +7619,13 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7626,10 +7636,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7640,7 +7650,7 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7652,17 +7662,19 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>448</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7687,13 +7699,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>448</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>449</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7711,13 +7723,13 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>83</v>
@@ -7729,13 +7741,13 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>83</v>
+        <v>441</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>452</v>
+        <v>308</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7746,10 +7758,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7772,16 +7784,18 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>325</v>
+        <v>451</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7829,7 +7843,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7850,10 +7864,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>425</v>
+        <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7864,10 +7878,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7878,7 +7892,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7887,20 +7901,18 @@
         <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L50" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>461</v>
-      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7949,13 +7961,13 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>83</v>
@@ -7970,10 +7982,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>462</v>
+        <v>428</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -7984,10 +7996,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8010,16 +8022,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8069,7 +8081,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8090,10 +8102,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8104,10 +8116,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8130,20 +8142,18 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>405</v>
+        <v>468</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>474</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8191,7 +8201,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8212,10 +8222,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8226,10 +8236,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8240,7 +8250,7 @@
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>83</v>
@@ -8249,19 +8259,23 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>325</v>
+        <v>408</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>326</v>
+        <v>474</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8309,19 +8323,19 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>328</v>
+        <v>473</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>83</v>
@@ -8330,10 +8344,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>83</v>
+        <v>478</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>329</v>
+        <v>479</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8344,21 +8358,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8370,17 +8384,15 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M54" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N54" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8429,19 +8441,19 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>83</v>
@@ -8453,7 +8465,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8464,14 +8476,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>416</v>
+        <v>139</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8484,26 +8496,24 @@
         <v>83</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>417</v>
+        <v>141</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>418</v>
+        <v>335</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O55" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8551,7 +8561,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>419</v>
+        <v>338</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8575,7 +8585,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8586,45 +8596,45 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>481</v>
+        <v>420</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>482</v>
+        <v>421</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>483</v>
+        <v>143</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8649,13 +8659,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>211</v>
+        <v>83</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8673,34 +8683,34 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>215</v>
+        <v>137</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -8708,10 +8718,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8719,7 +8729,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>94</v>
@@ -8734,19 +8744,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="L57" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="O57" t="s" s="2">
-        <v>278</v>
+        <v>211</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8771,13 +8781,13 @@
         <v>83</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>83</v>
@@ -8795,10 +8805,10 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>94</v>
@@ -8813,27 +8823,27 @@
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>281</v>
+        <v>218</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>282</v>
+        <v>219</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>283</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8853,22 +8863,22 @@
         <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>192</v>
+        <v>489</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="O58" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -8893,13 +8903,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -8917,7 +8927,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8926,7 +8936,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>292</v>
+        <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -8935,38 +8945,38 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>83</v>
+        <v>492</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>83</v>
@@ -8981,16 +8991,16 @@
         <v>192</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>296</v>
+        <v>494</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>297</v>
+        <v>495</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>298</v>
+        <v>496</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9015,13 +9025,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9039,16 +9049,16 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9057,31 +9067,31 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>302</v>
+        <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>303</v>
+        <v>137</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>305</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9100,19 +9110,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>496</v>
+        <v>300</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>497</v>
+        <v>301</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>408</v>
+        <v>302</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>409</v>
+        <v>303</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9137,13 +9147,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9161,7 +9171,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9179,23 +9189,145 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AO60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP60" t="s" s="2">
+      <c r="P61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP60">
+  <autoFilter ref="A1:AP61">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9205,7 +9337,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI59">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
